--- a/docs/weekly/2026-07-4주차/C-lab_PoC_WBS_v8.xlsx
+++ b/docs/weekly/2026-07-4주차/C-lab_PoC_WBS_v8.xlsx
@@ -709,7 +709,7 @@
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>v8 (2026-07-20: 07-4주차 — DeepStream 다채널 전환/16ch@5fps; 4.7.1·4.7.2·4.2.3 완료, 4.7.3·4.7.4·6.3.2 진행중)</t>
+          <t>v8 (2026-07-20: 07-4주차 — DeepStream 다채널 전환/16ch@5fps; 4.7.1·4.7.2·4.2.3 완료, 4.7.3·4.7.4·6.3.2 진행중) · 최종 스케일 목표 150→50~60ch 하향(GPU 3~4장)</t>
         </is>
       </c>
       <c r="D5" s="24" t="n"/>
@@ -4215,12 +4215,12 @@
       <c r="C74" s="30" t="n"/>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>150채널 스케일 달성: 대규모 동시 처리, VRAM/CPU 자원 최적화, 추적 경량화, GPU 증설 전제 검토</t>
+          <t>50~60채널 스케일 달성: 대규모 동시 처리, VRAM/CPU 자원 최적화, GPU 3~4장 증설 전제(1GPU 16ch@5fps 실측 기반), 필요 시 추적 경량화</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>150채널 스케일 처리(목표 fps)</t>
+          <t>50~60채널 스케일 처리(목표 fps)</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
